--- a/htr-FHIR/ig/ValueSet-fr-doc-vs-savoir-faire-role.xlsx
+++ b/htr-FHIR/ig/ValueSet-fr-doc-vs-savoir-faire-role.xlsx
@@ -71,7 +71,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T13:52:25+00:00</t>
+    <t>2025-03-25T14:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
